--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/atacama.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/atacama.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>11556.92</v>
+        <v>11699.16</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,68 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>13963.93</v>
+        <v>13993.69</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1197-97-CM26</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Transporte Corporativo Infinity</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>76.207.531-8</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>15278.84</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/atacama.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/atacama.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Atacama" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Atacama" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -694,6 +694,189 @@
         <v>15278.84</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1197-99-CM26</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>CAR PLACE SPA</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>76.704.974-9</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>27355.86</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1208093-61-CM26</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>62.000.890-7</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>arriendo</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>99.501.690-7</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>4375.46</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1197-107-CM26</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Felipe </t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>76.834.013-7</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>1452.68</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/atacama.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/atacama.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -877,6 +877,128 @@
         <v>1452.68</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1197-122-CM26</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Transporte Corporativo Infinity</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>76.207.531-8</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>8555.75</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1197-123-CM26</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Transporte Corporativo Infinity</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>76.207.531-8</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>6260.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/atacama.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/atacama.xlsx
@@ -900,7 +900,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">

--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/atacama.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/atacama.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
